--- a/astro-site/public/dl/restaurant-checklist-templates/BONUS-01-pre-shift-meeting-template.xlsx
+++ b/astro-site/public/dl/restaurant-checklist-templates/BONUS-01-pre-shift-meeting-template.xlsx
@@ -620,7 +620,7 @@
     <row r="12" ht="31" customHeight="1">
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the FRAME of the day.</t>
+          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the BACKBONE of the day.</t>
         </is>
       </c>
     </row>
